--- a/data/trans_orig/Predimed-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Predimed-Clase-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media de la escala de adherencia a la dieta mediterránea (Predimed)</t>
+          <t>Puntuación media de la escala de adherencia a la dieta mediterránea (Predimed) (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,47; 6,89</t>
+          <t>6,46; 6,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,63; 6,92</t>
+          <t>6,63; 6,91</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 6,66</t>
+          <t>6,2; 6,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,56; 6,98</t>
+          <t>6,55; 6,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,42; 6,73</t>
+          <t>6,43; 6,75</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,34; 6,91</t>
+          <t>6,35; 6,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 7,14</t>
+          <t>6,55; 7,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,49; 6,91</t>
+          <t>6,48; 6,91</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,18; 6,55</t>
+          <t>6,19; 6,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,58; 7,51</t>
+          <t>6,59; 7,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,46; 7,13</t>
+          <t>6,46; 7,08</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,91; 6,4</t>
+          <t>5,91; 6,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,29; 7,06</t>
+          <t>6,28; 7,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,22; 6,72</t>
+          <t>6,21; 6,67</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,51; 6,41</t>
+          <t>5,55; 6,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,63; 5,93</t>
+          <t>5,62; 5,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,67; 5,96</t>
+          <t>5,67; 5,98</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,33; 6,56</t>
+          <t>6,32; 6,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,43; 6,84</t>
+          <t>6,44; 6,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,4; 6,65</t>
+          <t>6,41; 6,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Predimed-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Predimed-Clase-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,69</t>
+          <t>6,68</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,88</t>
+          <t>6,85</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,78</t>
+          <t>6,76</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,46; 6,89</t>
+          <t>6,45; 6,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,71; 7,06</t>
+          <t>6,68; 7,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,63; 6,91</t>
+          <t>6,63; 6,9</t>
         </is>
       </c>
     </row>
@@ -603,12 +603,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,77</t>
+          <t>6,75</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,58</t>
+          <t>6,57</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,2; 6,66</t>
+          <t>6,18; 6,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 6,97</t>
+          <t>6,55; 6,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,43; 6,75</t>
+          <t>6,41; 6,73</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6,65</t>
+          <t>6,45</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,86</t>
+          <t>6,81</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,69</t>
+          <t>6,55</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,35; 6,89</t>
+          <t>6,22; 6,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,55; 7,16</t>
+          <t>6,51; 7,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,48; 6,91</t>
+          <t>6,35; 6,72</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>6,39</t>
+          <t>6,42</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,93</t>
+          <t>6,6</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,66</t>
+          <t>6,5</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,19; 6,57</t>
+          <t>6,25; 6,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,59; 7,46</t>
+          <t>6,46; 6,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,46; 7,08</t>
+          <t>6,39; 6,62</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6,13</t>
+          <t>6,06</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,5</t>
+          <t>6,31</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,37</t>
+          <t>6,21</t>
         </is>
       </c>
     </row>
@@ -771,24 +771,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,91; 6,36</t>
+          <t>5,84; 6,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,28; 7,0</t>
+          <t>6,18; 6,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,21; 6,67</t>
+          <t>6,09; 6,33</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -798,17 +798,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>5,97</t>
+          <t>5,65</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5,78</t>
+          <t>5,75</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5,82</t>
+          <t>5,73</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,55; 6,39</t>
+          <t>5,23; 6,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,62; 5,94</t>
+          <t>5,6; 5,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,67; 5,98</t>
+          <t>5,57; 5,87</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>6,43</t>
+          <t>6,36</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6,57</t>
+          <t>6,41</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,5</t>
+          <t>6,38</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,32; 6,58</t>
+          <t>6,27; 6,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,44; 6,85</t>
+          <t>6,34; 6,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,41; 6,69</t>
+          <t>6,33; 6,44</t>
         </is>
       </c>
     </row>
